--- a/info待确认与弃用_10.8.xlsx
+++ b/info待确认与弃用_10.8.xlsx
@@ -616,7 +616,9 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>18/44 个CID置非零：8200 0x30b=32/0x310=32/0x311=32/0x331=32/0x335=32, 9000 0x20000015=8/0x20000018=8/0x20000024=8/0x2000003c=8, 9200 0x2000003a=64, 9400 0x334=8/0x2000002b=8/0x20000035=8/0x20000036=8/0x2000003b=8, dcnano 0x20000003=64/0x20000017=64/0x20000020=64</t>
+          <t>13/33 个CID置非零（按取值分组，不含8200系列）：
+8: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
+64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -655,7 +657,18 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>44/44 个CID置非零：8200 0x30b={4096×4, 64×2}/0x310={4096×6, 64×2}/0x311={4096×6, 64×2}/0x31b=4096/0x325=2048/0x331={4096×3, 128×1}/0x333=4096/0x335={4096×6, 128×2}/0x20000008=4096/0x2000002e=4096/0x2000003e=2160, 9000 0x20000015={4096×2, 256×1}/0x20000018={4096×3, 256×1}/0x2000001b=4096/0x20000024={4096×3, 256×1}/0x2000003c={4096×3, 256×1}, 9200 0x323=8192/0x2000000a=4096/0x20000014=4096/0x20000021=4096/0x20000028=4096/0x2000002d=4096/0x20000037=4096/0x2000003a={3840×6, 64×1}, 9400 0x316=8192/0x326={8192×4, 2880×4}/0x327={8192×4, 2880×4}/0x329={9500×4, 2560×4}/0x32a=8192/0x334={7680×8, 256×4}/0x20000005=8192/0x2000000b=8192/0x2000001a=8192/0x20000026=4096/0x2000002b={4096×4, 256×3}/0x20000034=4096/0x20000035={4096×8, 256×4}/0x20000036={5120×8, 256×4}/0x20000039=4096/0x2000003b={4096×8, 256×4}/0x2000003d=4096, dcnano 0x20000003={1920×4, 64×1}/0x20000017={2560×1, 64×1}/0x20000020={1920×4, 64×1}</t>
+          <t>33/33 个CID置非零（按取值分组，不含8200系列）：
+64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020
+256: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
+1920: 0x20000003, 0x20000020
+2560: 0x329, 0x20000017
+2880: 0x326, 0x327
+3840: 0x2000003a
+4096: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000039, 0x2000003b, 0x2000003d
+5120: 0x20000036
+7680: 0x334
+8192: 0x323, 0x316, 0x326, 0x327, 0x32a, 0x20000005, 0x2000000b, 0x2000001a
+9500: 0x329</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -694,7 +707,16 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>44/44 个CID置非零：8200 0x30b={4096×4, 64×2}/0x310={4096×6, 64×2}/0x311={4096×6, 64×2}/0x31b=4096/0x325=2048/0x331={4096×3, 128×1}/0x333=4096/0x335={4096×6, 128×2}/0x20000008=4096/0x2000002e=4096/0x2000003e=2160, 9000 0x20000015={4096×2, 256×1}/0x20000018={4096×3, 256×1}/0x2000001b=4096/0x20000024={4320×3, 256×1}/0x2000003c={4320×3, 256×1}, 9200 0x323=4320/0x2000000a=4096/0x20000014=4096/0x20000021=4096/0x20000028=4096/0x2000002d=4320/0x20000037=8680/0x2000003a={2160×6, 64×1}, 9400 0x316=4320/0x326=4320/0x327=4320/0x329=4320/0x32a=4320/0x334={4320×8, 256×4}/0x20000005=4320/0x2000000b=4320/0x2000001a=4320/0x20000026=8192/0x2000002b={4320×4, 256×3}/0x20000034=4320/0x20000035={4320×8, 256×4}/0x20000036={4320×8, 256×4}/0x20000039=4320/0x2000003b={4320×8, 256×4}/0x2000003d=4320, dcnano 0x20000003={1080×4, 64×1}/0x20000017={1440×1, 64×1}/0x20000020={1080×4, 64×1}</t>
+          <t>33/33 个CID置非零（按取值分组，不含8200系列）：
+64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020
+256: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
+1080: 0x20000003, 0x20000020
+1440: 0x20000017
+2160: 0x2000003a
+4096: 0x20000015, 0x20000018, 0x2000001b, 0x2000000a, 0x20000014, 0x20000021, 0x20000028
+4320: 0x20000024, 0x2000003c, 0x323, 0x2000002d, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+8192: 0x20000026
+8680: 0x20000037</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -721,7 +743,7 @@
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>0/44，无任何CID写过</t>
+          <t>0/33，无任何CID写过</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
@@ -756,7 +778,9 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>44/44 个CID置非零：8200 0x30b=true/0x310=true/0x311=true/0x31b=true/0x325=true/0x331=true/0x333=true/0x335=true/0x20000008=true/0x2000002e=true/0x2000003e=true, 9000 0x20000015=1/0x20000018=1/0x2000001b=1/0x20000024=1/0x2000003c=1, 9200 0x323=1/0x2000000a=1/0x20000014=1/0x20000021=1/0x20000028=1/0x2000002d=1/0x20000037=1/0x2000003a=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1/0x20000026=1/0x2000002b=1/0x20000034=1/0x20000035=1/0x20000036=1/0x20000039=1/0x2000003b=1/0x2000003d=1, dcnano 0x20000003=true/0x20000017=true/0x20000020=true</t>
+          <t>33/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+true: 0x20000003, 0x20000017, 0x20000020</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -795,7 +819,8 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>10/44 个CID置非零：9000 0x20000015=1/0x20000018=1/0x20000024=1/0x2000003c=1, 9200 0x20000014=1/0x20000021=1/0x20000028=1, 9400 0x2000002b=1/0x20000036=1/0x2000003b=1</t>
+          <t>10/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x20000014, 0x20000021, 0x20000028, 0x2000002b, 0x20000036, 0x2000003b</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -834,7 +859,8 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>1/44 个CID置非零：9200 0x20000021=1</t>
+          <t>1/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000021</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -873,7 +899,8 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>3/44 个CID置非零：9000 0x20000024=1/0x2000003c=1, 9200 0x2000003a=1</t>
+          <t>3/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000024, 0x2000003c, 0x2000003a</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -912,7 +939,8 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2/44 个CID置非零：9400 0x2000000b=1/0x2000001a=1</t>
+          <t>2/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -951,7 +979,8 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>1/44 个CID置非零：9400 0x2000001a=1</t>
+          <t>1/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000001a</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -990,7 +1019,8 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2/44 个CID置非零：9400 0x2000000b=1/0x2000001a=1</t>
+          <t>2/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1029,7 +1059,8 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>1/44 个CID置非零：9400 0x2000001a=1</t>
+          <t>1/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000001a</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1068,7 +1099,8 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>1/44 个CID置非零：9400 0x2000001a=1</t>
+          <t>1/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000001a</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -1107,7 +1139,8 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>8/44 个CID置非零：9200 0x20000028=1/0x20000037=1/0x2000003a=1, 9400 0x2000002b=1/0x20000035=1/0x20000036=1/0x20000039=1/0x2000003b=1</t>
+          <t>8/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000028, 0x20000037, 0x2000003a, 0x2000002b, 0x20000035, 0x20000036, 0x20000039, 0x2000003b</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1146,7 +1179,8 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>1/41 个CID置非零：9400 0x2000001a=8</t>
+          <t>1/30 个CID置非零（按取值分组，不含8200系列）：
+8: 0x2000001a</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -1185,7 +1219,8 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>1/41 个CID置非零：9400 0x2000001a=1280</t>
+          <t>1/30 个CID置非零（按取值分组，不含8200系列）：
+1280: 0x2000001a</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -1224,7 +1259,8 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>2/41 个CID置非零：9400 0x2000000b=1/0x2000001a=1</t>
+          <t>2/30 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1251,7 +1287,9 @@
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>3/44 个CID置非零：9000 0x20000024=PALETTE_V1/0x2000003c=PALETTE_V1, 9200 0x2000003a=PALETTE_V2</t>
+          <t>3/33 个CID置非零（按取值分组，不含8200系列）：
+PALETTE_V1: 0x20000024, 0x2000003c
+PALETTE_V2: 0x2000003a</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
@@ -1286,7 +1324,8 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>10/44 个CID置非零：9400 0x316=&amp;dsc_enc_hw_config/0x326=&amp;dsc_enc_hw_config/0x327=&amp;dsc_enc_hw_config/0x329=&amp;dsc_enc_hw_config/0x32a=&amp;dsc_enc_hw_config/0x334=&amp;dsc_enc_hw_config/0x20000005=&amp;dsc_enc_hw_config/0x2000000b=&amp;dsc_enc_hw_config/0x2000001a=&amp;dsc_enc_hw_config/0x20000036=&amp;dsc_enc_hw_config</t>
+          <t>10/33 个CID置非零（按取值分组，不含8200系列）：
+&amp;dsc_enc_hw_config: 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000036</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1325,7 +1364,11 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>44/44 个CID置非零：8200 0x30b=128/0x310=128/0x311=128/0x31b=128/0x325=128/0x331=128/0x333=128/0x335=128/0x20000008=128/0x2000002e=128/0x2000003e=128, 9000 0x20000015=64/0x20000018=64/0x2000001b=64/0x20000024=64/0x2000003c=64, 9200 0x323=64/0x2000000a=64/0x20000014=64/0x20000021=64/0x20000028=64/0x2000002d=64/0x20000037=64/0x2000003a=64, 9400 0x316=64/0x326=64/0x327=64/0x329=64/0x32a=64/0x334=256/0x20000005=32/0x2000000b=32/0x2000001a=32/0x20000026=64/0x2000002b=64/0x20000034=64/0x20000035=64/0x20000036=64/0x20000039=64/0x2000003b=64/0x2000003d=64, dcnano 0x20000003=128/0x20000017=128/0x20000020=128</t>
+          <t>33/33 个CID置非零（按取值分组，不含8200系列）：
+32: 0x20000005, 0x2000000b, 0x2000001a
+64: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+128: 0x20000003, 0x20000017, 0x20000020
+256: 0x334</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1364,7 +1407,9 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>44/44 个CID置非零：8200 0x30b=256/0x310=256/0x311=256/0x31b=256/0x325=256/0x331=256/0x333=256/0x335=256/0x20000008=256/0x2000002e=256/0x2000003e=256, 9000 0x20000015=256/0x20000018=256/0x2000001b=256/0x20000024=256/0x2000003c=256, 9200 0x323=256/0x2000000a=256/0x20000014=256/0x20000021=256/0x20000028=256/0x2000002d=256/0x20000037=256/0x2000003a=256, 9400 0x316=256/0x326=256/0x327=256/0x329=256/0x32a=256/0x334=256/0x20000005=32/0x2000000b=32/0x2000001a=32/0x20000026=256/0x2000002b=256/0x20000034=256/0x20000035=256/0x20000036=256/0x20000039=256/0x2000003b=256/0x2000003d=256, dcnano 0x20000003=256/0x20000017=256/0x20000020=256</t>
+          <t>33/33 个CID置非零（按取值分组，不含8200系列）：
+32: 0x20000005, 0x2000000b, 0x2000001a
+256: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d, 0x20000003, 0x20000017, 0x20000020</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1403,7 +1448,9 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>30/44 个CID置非零：9000 0x20000015=512/0x20000018=512/0x2000001b=512/0x20000024=512/0x2000003c=512, 9200 0x323=512/0x2000000a=512/0x20000014=512/0x20000021=512/0x20000028=512/0x2000002d=512/0x20000037=512/0x2000003a=512, 9400 0x316=512/0x326=512/0x327=512/0x329=512/0x32a=512/0x334=640/0x20000005=512/0x2000000b=512/0x2000001a=512/0x20000026=512/0x2000002b=512/0x20000034=512/0x20000035=512/0x20000036=512/0x20000039=512/0x2000003b=512/0x2000003d=512</t>
+          <t>30/33 个CID置非零（按取值分组，不含8200系列）：
+512: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+640: 0x334</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -1442,7 +1489,10 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>30/44 个CID置非零：9000 0x20000015=144/0x20000018=144/0x2000001b=144/0x20000024=144/0x2000003c=144, 9200 0x323=144/0x2000000a=144/0x20000014=144/0x20000021=144/0x20000028=144/0x2000002d=144/0x20000037=144/0x2000003a=120, 9400 0x316=144/0x326=144/0x327=144/0x329=144/0x32a=144/0x334=180/0x20000005=144/0x2000000b=144/0x2000001a=144/0x20000026=120/0x2000002b=120/0x20000034=120/0x20000035=120/0x20000036=120/0x20000039=120/0x2000003b=120/0x2000003d=120</t>
+          <t>30/33 个CID置非零（按取值分组，不含8200系列）：
+120: 0x2000003a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+144: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x20000005, 0x2000000b, 0x2000001a
+180: 0x334</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -1481,7 +1531,9 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>28/44 个CID置非零：9000 0x20000015=16/0x20000018=16/0x2000001b=10/0x20000024=10/0x2000003c=10, 9200 0x323=10/0x20000014=16/0x20000021=16/0x20000028=10/0x2000002d=10/0x2000003a=10, 9400 0x316=10/0x326=10/0x327=10/0x329=10/0x32a=10/0x334=10/0x20000005=10/0x2000000b=10/0x2000001a=10/0x20000026=10/0x2000002b=10/0x20000034=10/0x20000035=10/0x20000036=10/0x20000039=10/0x2000003b=10/0x2000003d=10</t>
+          <t>28/33 个CID置非零（按取值分组，不含8200系列）：
+10: 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+16: 0x20000015, 0x20000018, 0x20000014, 0x20000021</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1520,7 +1572,8 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>23/44 个CID置非零：9000 0x20000024=129/0x2000003c=129, 9200 0x323=129/0x20000028=129/0x2000002d=129/0x2000003a=129, 9400 0x316=129/0x326=129/0x327=129/0x329=129/0x32a=129/0x334=129/0x20000005=129/0x2000000b=129/0x2000001a=129/0x20000026=129/0x2000002b=129/0x20000034=129/0x20000035=129/0x20000036=129/0x20000039=129/0x2000003b=129/0x2000003d=129</t>
+          <t>23/33 个CID置非零（按取值分组，不含8200系列）：
+129: 0x20000024, 0x2000003c, 0x323, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -1559,7 +1612,8 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>23/44 个CID置非零：9000 0x20000024=33/0x2000003c=33, 9200 0x323=33/0x20000028=33/0x2000002d=33/0x2000003a=33, 9400 0x316=33/0x326=33/0x327=33/0x329=33/0x32a=33/0x334=33/0x20000005=33/0x2000000b=33/0x2000001a=33/0x20000026=33/0x2000002b=33/0x20000034=33/0x20000035=33/0x20000036=33/0x20000039=33/0x2000003b=33/0x2000003d=33</t>
+          <t>23/33 个CID置非零（按取值分组，不含8200系列）：
+33: 0x20000024, 0x2000003c, 0x323, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -1598,7 +1652,8 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>28/44 个CID置非零：8200 0x31b=DEGAMMA_SIZE/0x325=DEGAMMA_SIZE/0x2000002e=DEGAMMA_SIZE/0x2000003e=DEGAMMA_SIZE, 9000 0x20000015=129/0x20000018=129, 9200 0x323=129/0x20000014=129/0x20000021=129/0x20000028=129/0x2000003a=129, 9400 0x316=129/0x326=129/0x327=129/0x329=129/0x32a=129/0x334=129/0x20000005=129/0x2000000b=129/0x2000001a=129/0x20000026=129/0x2000002b=129/0x20000034=129/0x20000035=129/0x20000036=129/0x20000039=129/0x2000003b=129/0x2000003d=129</t>
+          <t>24/33 个CID置非零（按取值分组，不含8200系列）：
+129: 0x20000015, 0x20000018, 0x323, 0x20000014, 0x20000021, 0x20000028, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1637,7 +1692,10 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>42/44 个CID置非零：8200 0x30b=GAMMA_SIZE/0x310=GAMMA_SIZE/0x311=GAMMA_SIZE/0x31b=GAMMA_SIZE/0x325=GAMMA_SIZE/0x331=GAMMA_SIZE/0x333=GAMMA_SIZE/0x335=GAMMA_SIZE/0x20000008=GAMMA_SIZE/0x2000002e=GAMMA_SIZE/0x2000003e=GAMMA_SIZE, 9000 0x20000015=257/0x20000018=257/0x2000001b=257/0x20000024=257/0x2000003c=257, 9200 0x323=129/0x20000014=257/0x20000021=257/0x20000028=257/0x2000002d=257/0x2000003a=257, 9400 0x316=257/0x326=129/0x327=129/0x329=129/0x32a=257/0x334=257/0x20000005=257/0x2000000b=257/0x2000001a=257/0x20000026=257/0x2000002b=257/0x20000034=257/0x20000035=257/0x20000036=257/0x20000039=257/0x2000003b=257/0x2000003d=257, dcnano 0x20000003=GAMMA_SIZE/0x20000017=GAMMA_SIZE/0x20000020=GAMMA_SIZE</t>
+          <t>31/33 个CID置非零（按取值分组，不含8200系列）：
+129: 0x323, 0x326, 0x327, 0x329
+257: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+GAMMA_SIZE: 0x20000003, 0x20000017, 0x20000020</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -1676,7 +1734,8 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>4/44 个CID置非零：9200 0x2000003a=65, 9400 0x20000034=65/0x20000039=65/0x2000003d=65</t>
+          <t>4/33 个CID置非零（按取值分组，不含8200系列）：
+65: 0x2000003a, 0x20000034, 0x20000039, 0x2000003d</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -1715,7 +1774,10 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>11/44 个CID置非零：9000 0x20000015=12/0x20000018=12, 9200 0x20000014=12/0x20000021=12/0x2000003a=17, 9400 0x2000000b=16/0x2000001a=16/0x20000034=17/0x20000039=17/0x2000003b=17/0x2000003d=17</t>
+          <t>11/33 个CID置非零（按取值分组，不含8200系列）：
+12: 0x20000015, 0x20000018, 0x20000014, 0x20000021
+16: 0x2000000b, 0x2000001a
+17: 0x2000003a, 0x20000034, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -1754,7 +1816,9 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>9/44 个CID置非零：9200 0x2000003a=17, 9400 0x2000000b=14/0x2000001a=14/0x20000034=17/0x20000035=17/0x20000036=17/0x20000039=17/0x2000003b=17/0x2000003d=17</t>
+          <t>9/33 个CID置非零（按取值分组，不含8200系列）：
+14: 0x2000000b, 0x2000001a
+17: 0x2000003a, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -1793,7 +1857,8 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2/44 个CID置非零：9400 0x2000000b=14/0x2000001a=14</t>
+          <t>2/33 个CID置非零（按取值分组，不含8200系列）：
+14: 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -1832,7 +1897,8 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>23/44 个CID置非零：9000 0x20000024=12/0x2000003c=12, 9200 0x323=12/0x20000028=12/0x2000002d=12/0x2000003a=12, 9400 0x316=12/0x326=12/0x327=12/0x329=12/0x32a=12/0x334=12/0x20000005=12/0x2000000b=12/0x2000001a=12/0x20000026=12/0x2000002b=12/0x20000034=12/0x20000035=12/0x20000036=12/0x20000039=12/0x2000003b=12/0x2000003d=12</t>
+          <t>23/33 个CID置非零（按取值分组，不含8200系列）：
+12: 0x20000024, 0x2000003c, 0x323, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -1871,7 +1937,8 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>23/44 个CID置非零：9000 0x20000024=24/0x2000003c=24, 9200 0x323=24/0x20000028=24/0x2000002d=24/0x2000003a=24, 9400 0x316=24/0x326=24/0x327=24/0x329=24/0x32a=24/0x334=24/0x20000005=24/0x2000000b=24/0x2000001a=24/0x20000026=24/0x2000002b=24/0x20000034=24/0x20000035=24/0x20000036=24/0x20000039=24/0x2000003b=24/0x2000003d=24</t>
+          <t>23/33 个CID置非零（按取值分组，不含8200系列）：
+24: 0x20000024, 0x2000003c, 0x323, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1910,7 +1977,9 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>23/44 个CID置非零：9000 0x20000024=24/0x2000003c=24, 9200 0x323=24/0x20000028=12/0x2000002d=24/0x2000003a=12, 9400 0x316=24/0x326=24/0x327=24/0x329=24/0x32a=24/0x334=24/0x20000005=24/0x2000000b=24/0x2000001a=24/0x20000026=24/0x2000002b=12/0x20000034=12/0x20000035=12/0x20000036=12/0x20000039=12/0x2000003b=12/0x2000003d=12</t>
+          <t>23/33 个CID置非零（按取值分组，不含8200系列）：
+12: 0x20000028, 0x2000003a, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+24: 0x20000024, 0x2000003c, 0x323, 0x2000002d, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -1949,7 +2018,9 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>24/44 个CID置非零：9000 0x20000015=12/0x20000018=12, 9200 0x323=10/0x20000014=12/0x20000021=12/0x20000028=12/0x2000003a=10, 9400 0x316=10/0x326=10/0x327=10/0x329=10/0x32a=10/0x334=10/0x20000005=10/0x2000000b=10/0x2000001a=10/0x20000026=12/0x2000002b=10/0x20000034=10/0x20000035=10/0x20000036=10/0x20000039=10/0x2000003b=10/0x2000003d=10</t>
+          <t>24/33 个CID置非零（按取值分组，不含8200系列）：
+10: 0x323, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
+12: 0x20000015, 0x20000018, 0x20000014, 0x20000021, 0x20000028, 0x20000026</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -1988,7 +2059,8 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>31/44 个CID置非零：8200 0x311=10/0x31b=10/0x325=10/0x333=10/0x2000002e=10/0x2000003e=10, 9000 0x20000015=14/0x20000018=14/0x20000024=14/0x2000003c=14, 9200 0x323=14/0x20000014=14/0x20000021=14/0x20000028=14/0x2000002d=14, 9400 0x316=14/0x326=14/0x327=14/0x329=14/0x32a=14/0x334=14/0x20000005=14/0x2000000b=14/0x2000001a=14/0x2000002b=14/0x20000034=14/0x20000035=14/0x20000036=14/0x20000039=14/0x2000003b=14/0x2000003d=14</t>
+          <t>25/33 个CID置非零（按取值分组，不含8200系列）：
+14: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x323, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -2027,7 +2099,8 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>9/44 个CID置非零：9000 0x20000015=12/0x20000018=12, 9200 0x20000014=12/0x20000021=12/0x20000028=12/0x2000003a=12, 9400 0x20000034=12/0x20000039=12/0x2000003d=12</t>
+          <t>9/33 个CID置非零（按取值分组，不含8200系列）：
+12: 0x20000015, 0x20000018, 0x20000014, 0x20000021, 0x20000028, 0x2000003a, 0x20000034, 0x20000039, 0x2000003d</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -2066,7 +2139,9 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>9/44 个CID置非零：9000 0x20000015=14/0x20000018=14, 9200 0x20000014=14/0x20000021=14/0x20000028=14/0x2000003a=17, 9400 0x20000034=17/0x20000039=17/0x2000003d=17</t>
+          <t>9/33 个CID置非零（按取值分组，不含8200系列）：
+14: 0x20000015, 0x20000018, 0x20000014, 0x20000021, 0x20000028
+17: 0x2000003a, 0x20000034, 0x20000039, 0x2000003d</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -2105,7 +2180,8 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>4/44 个CID置非零：9200 0x2000003a=12, 9400 0x20000034=12/0x20000039=12/0x2000003d=12</t>
+          <t>4/33 个CID置非零（按取值分组，不含8200系列）：
+12: 0x2000003a, 0x20000034, 0x20000039, 0x2000003d</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -2144,7 +2220,10 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>7/44 个CID置非零：9400 0x32a=0xF/0x20000005=0xF/0x2000000b=0xF/0x2000001a=0xF/0x20000034=0x03/0x20000039=0x03/0x2000003b=0x1</t>
+          <t>7/33 个CID置非零（按取值分组，不含8200系列）：
+0x1: 0x2000003b
+0x03: 0x20000034, 0x20000039
+0xF: 0x32a, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -2183,7 +2262,8 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>6/44 个CID置非零：9200 0x20000028=3/0x2000003a=3, 9400 0x20000034=3/0x20000039=3/0x2000003b=3/0x2000003d=3</t>
+          <t>6/33 个CID置非零（按取值分组，不含8200系列）：
+3: 0x20000028, 0x2000003a, 0x20000034, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -2222,7 +2302,8 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>27/44 个CID置非零：9000 0x20000015=1/0x20000018=1/0x2000001b=1/0x20000024=1/0x2000003c=1, 9200 0x323=1/0x2000000a=1/0x20000014=1/0x20000021=1/0x20000028=1/0x2000002d=1/0x20000037=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x20000005=1/0x2000000b=1/0x2000001a=1/0x20000026=1/0x2000002b=1/0x20000034=1/0x20000035=1/0x20000036=1/0x2000003b=1/0x2000003d=1</t>
+          <t>27/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -2261,7 +2342,8 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>4/44 个CID置非零：9400 0x2000002b=1/0x20000035=1/0x20000036=1/0x2000003b=1</t>
+          <t>4/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000002b, 0x20000035, 0x20000036, 0x2000003b</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -2300,7 +2382,8 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>1/44 个CID置非零：9400 0x2000002b=0x1</t>
+          <t>1/33 个CID置非零（按取值分组，不含8200系列）：
+0x1: 0x2000002b</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2339,7 +2422,8 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>2/44 个CID置非零：9400 0x20000034=0x7/0x20000039=0x7</t>
+          <t>2/33 个CID置非零（按取值分组，不含8200系列）：
+0x7: 0x20000034, 0x20000039</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2444,7 +2528,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>0/44，无任何CID写过</t>
+          <t>0/33，无任何CID写过</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr"/>
@@ -2478,7 +2562,8 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>29/44 个CID置非零：9000 0x20000015=1/0x20000018=1/0x2000001b=1/0x20000024=1/0x2000003c=1, 9200 0x323=1/0x2000000a=1/0x20000014=1/0x20000021=1/0x20000028=1/0x2000002d=1/0x20000037=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1/0x20000026=1/0x2000002b=1/0x20000034=1/0x20000035=1/0x20000036=1/0x20000039=1/0x2000003b=1/0x2000003d=1</t>
+          <t>29/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr"/>
@@ -2512,7 +2597,8 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>12/44 个CID置非零：9000 0x20000024=1/0x2000003c=1, 9200 0x323=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1</t>
+          <t>12/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000024, 0x2000003c, 0x323, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
@@ -2546,7 +2632,8 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>20/44 个CID置非零：9000 0x20000024=1/0x2000003c=1, 9200 0x323=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1/0x20000026=1/0x2000002b=1/0x20000034=1/0x20000035=1/0x20000036=1/0x20000039=1/0x2000003b=1/0x2000003d=1</t>
+          <t>20/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000024, 0x2000003c, 0x323, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
@@ -2580,7 +2667,8 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>21/44 个CID置非零：9000 0x20000015=1/0x20000018=1/0x20000024=1/0x2000003c=1, 9200 0x2000000a=1/0x20000014=1/0x20000021=1/0x20000028=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1/0x2000002b=1/0x20000035=1/0x20000036=1/0x2000003b=1</t>
+          <t>21/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
@@ -2614,7 +2702,8 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>6/44 个CID置非零：9200 0x323=1, 9400 0x316=1/0x32a=1/0x20000005=1/0x2000000b=1/0x2000001a=1</t>
+          <t>6/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x323, 0x316, 0x32a, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr"/>
@@ -2648,7 +2737,9 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>30/44 个CID置非零：9000 0x20000015=2/0x20000018=2/0x2000001b=2/0x20000024=2/0x2000003c=2, 9200 0x323=2/0x2000000a=2/0x20000014=2/0x20000021=2/0x20000028=2/0x2000002d=2/0x20000037=2/0x2000003a=2, 9400 0x316=14/0x326=2/0x327=2/0x329=2/0x32a=14/0x334=2/0x20000005=14/0x2000000b=14/0x2000001a=14/0x20000026=14/0x2000002b=14/0x20000034=14/0x20000035=14/0x20000036=14/0x20000039=14/0x2000003b=14/0x2000003d=14</t>
+          <t>30/33 个CID置非零（按取值分组，不含8200系列）：
+2: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x326, 0x327, 0x329, 0x334
+14: 0x316, 0x32a, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
@@ -2682,7 +2773,8 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>9/41 个CID置非零：9000 0x2000001b=1, 9200 0x323=1/0x2000000a=1/0x20000037=1, 9400 0x316=1/0x32a=1/0x20000005=1/0x2000000b=1/0x2000001a=1</t>
+          <t>9/30 个CID置非零（按取值分组，不含8200系列）：
+1: 0x2000001b, 0x323, 0x2000000a, 0x20000037, 0x316, 0x32a, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
@@ -2716,7 +2808,8 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>10/44 个CID置非零：9200 0x323=729, 9400 0x316=729/0x326=729/0x327=729/0x329=729/0x32a=729/0x334=729/0x20000005=729/0x2000000b=729/0x2000001a=729</t>
+          <t>10/33 个CID置非零（按取值分组，不含8200系列）：
+729: 0x323, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
@@ -2750,7 +2843,8 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>10/44 个CID置非零：9200 0x323=1, 9400 0x316=1/0x326=1/0x327=1/0x329=1/0x32a=1/0x334=1/0x20000005=1/0x2000000b=1/0x2000001a=1</t>
+          <t>10/33 个CID置非零（按取值分组，不含8200系列）：
+1: 0x323, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr"/>

--- a/info待确认与弃用_10.8.xlsx
+++ b/info待确认与弃用_10.8.xlsx
@@ -618,7 +618,7 @@
         <is>
           <t>13/33 个CID置非零（按取值分组，不含8200系列）：
 8: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
-64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020</t>
+64: 0x2000003a, 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -658,10 +658,10 @@
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>33/33 个CID置非零（按取值分组，不含8200系列）：
-64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020
+64: 0x2000003a, 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)
 256: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
-1920: 0x20000003, 0x20000020
-2560: 0x329, 0x20000017
+1920: 0x20000003(nano), 0x20000020(nano)
+2560: 0x329, 0x20000017(nano)
 2880: 0x326, 0x327
 3840: 0x2000003a
 4096: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000039, 0x2000003b, 0x2000003d
@@ -708,10 +708,10 @@
       <c r="F5" s="8" t="inlineStr">
         <is>
           <t>33/33 个CID置非零（按取值分组，不含8200系列）：
-64: 0x2000003a, 0x20000003, 0x20000017, 0x20000020
+64: 0x2000003a, 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)
 256: 0x20000015, 0x20000018, 0x20000024, 0x2000003c, 0x334, 0x2000002b, 0x20000035, 0x20000036, 0x2000003b
-1080: 0x20000003, 0x20000020
-1440: 0x20000017
+1080: 0x20000003(nano), 0x20000020(nano)
+1440: 0x20000017(nano)
 2160: 0x2000003a
 4096: 0x20000015, 0x20000018, 0x2000001b, 0x2000000a, 0x20000014, 0x20000021, 0x20000028
 4320: 0x20000024, 0x2000003c, 0x323, 0x2000002d, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
@@ -780,7 +780,7 @@
         <is>
           <t>33/33 个CID置非零（按取值分组，不含8200系列）：
 1: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
-true: 0x20000003, 0x20000017, 0x20000020</t>
+true: 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1367,7 +1367,7 @@
           <t>33/33 个CID置非零（按取值分组，不含8200系列）：
 32: 0x20000005, 0x2000000b, 0x2000001a
 64: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
-128: 0x20000003, 0x20000017, 0x20000020
+128: 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)
 256: 0x334</t>
         </is>
       </c>
@@ -1409,7 +1409,7 @@
         <is>
           <t>33/33 个CID置非零（按取值分组，不含8200系列）：
 32: 0x20000005, 0x2000000b, 0x2000001a
-256: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d, 0x20000003, 0x20000017, 0x20000020</t>
+256: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x323, 0x2000000a, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x20000037, 0x2000003a, 0x316, 0x326, 0x327, 0x329, 0x32a, 0x334, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d, 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
           <t>31/33 个CID置非零（按取值分组，不含8200系列）：
 129: 0x323, 0x326, 0x327, 0x329
 257: 0x20000015, 0x20000018, 0x2000001b, 0x20000024, 0x2000003c, 0x20000014, 0x20000021, 0x20000028, 0x2000002d, 0x2000003a, 0x316, 0x32a, 0x334, 0x20000005, 0x2000000b, 0x2000001a, 0x20000026, 0x2000002b, 0x20000034, 0x20000035, 0x20000036, 0x20000039, 0x2000003b, 0x2000003d
-GAMMA_SIZE: 0x20000003, 0x20000017, 0x20000020</t>
+GAMMA_SIZE: 0x20000003(nano), 0x20000017(nano), 0x20000020(nano)</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
